--- a/src/GunPla Models.xlsx
+++ b/src/GunPla Models.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7DB19EB-5F08-4AD0-9E78-F4966C7EB686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B1CBD8D-6205-49A9-AE59-F60BF957C982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAW" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="275">
   <si>
     <t>Grade / Line</t>
   </si>
@@ -246,6 +246,15 @@
     <t>After Colony (AC)</t>
   </si>
   <si>
+    <t>HGAC #211</t>
+  </si>
+  <si>
+    <t>OZ-06MS Leo</t>
+  </si>
+  <si>
+    <t>Leo</t>
+  </si>
+  <si>
     <t>HGAC #236</t>
   </si>
   <si>
@@ -258,506 +267,608 @@
     <t>HGAC #242</t>
   </si>
   <si>
+    <t>XXXG-01S</t>
+  </si>
+  <si>
+    <t>Shenlong Gundam</t>
+  </si>
+  <si>
+    <t>High Grade (HGCE) 1/144</t>
+  </si>
+  <si>
+    <t>HGCE #201</t>
+  </si>
+  <si>
+    <t>ZGMF-X20A</t>
+  </si>
+  <si>
+    <t>Strike Freedom Gundam</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam SEED DESTINY</t>
+  </si>
+  <si>
+    <t>High Grade (HGGQX) 1/144</t>
+  </si>
+  <si>
+    <t>HGGQX #01</t>
+  </si>
+  <si>
+    <t>GQuuuuux</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam GQuuuuuuX</t>
+  </si>
+  <si>
+    <t>Universal Century (Alternate)</t>
+  </si>
+  <si>
+    <t>High Grade (HGIBO) 1/144</t>
+  </si>
+  <si>
+    <t>HGIBO #001</t>
+  </si>
+  <si>
+    <t>ASW-G-08</t>
+  </si>
+  <si>
+    <t>Gundam Barbatos</t>
+  </si>
+  <si>
+    <t>IRON-BLOODED ORPHANS</t>
+  </si>
+  <si>
+    <t>Post Disaster (PD)</t>
+  </si>
+  <si>
+    <t>HGIBO #002</t>
+  </si>
+  <si>
+    <t>EB-06</t>
+  </si>
+  <si>
+    <t>Graze Standard / Commander</t>
+  </si>
+  <si>
+    <t>HGIBO #019</t>
+  </si>
+  <si>
+    <t>ASW-G-29</t>
+  </si>
+  <si>
+    <t>Gundam Astaroth</t>
+  </si>
+  <si>
+    <t>HGIBO #027</t>
+  </si>
+  <si>
+    <t>ASW-G-XX</t>
+  </si>
+  <si>
+    <t>Gundam Vidar</t>
+  </si>
+  <si>
+    <t>High Grade (HGUC) 1/144</t>
+  </si>
+  <si>
+    <t>HGUC #187</t>
+  </si>
+  <si>
+    <t>XM-X1</t>
+  </si>
+  <si>
+    <t>Crossbone Gundam X1</t>
+  </si>
+  <si>
+    <t>Mobile Suit Crossbone Gundam</t>
+  </si>
+  <si>
+    <t>HGUC #020</t>
+  </si>
+  <si>
+    <t>RGM-79</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>HGUC #056</t>
+  </si>
+  <si>
+    <t>RX-121-1 TR-1</t>
+  </si>
+  <si>
+    <t>Gundam TR-1 [Hazel]</t>
+  </si>
+  <si>
+    <t>HGUC #191</t>
+  </si>
+  <si>
+    <t>RX-78-2</t>
+  </si>
+  <si>
+    <t>RX-78-2 Gundam (Revive)</t>
+  </si>
+  <si>
+    <t>HGUC #038</t>
+  </si>
+  <si>
+    <t>RGM-79D</t>
+  </si>
+  <si>
+    <t>GM Cold Districts Type</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam 0080: War in the Pocket</t>
+  </si>
+  <si>
+    <t>HGUC #046</t>
+  </si>
+  <si>
+    <t>RGM-79G</t>
+  </si>
+  <si>
+    <t>GM Command</t>
+  </si>
+  <si>
+    <t>HGUC #051</t>
+  </si>
+  <si>
+    <t>RGM-79GS</t>
+  </si>
+  <si>
+    <t>GM Command Space Use</t>
+  </si>
+  <si>
+    <t>HGUC #146</t>
+  </si>
+  <si>
+    <t>RGM-79SD</t>
+  </si>
+  <si>
+    <t>GM Sniper II</t>
+  </si>
+  <si>
+    <t>HGUC #013</t>
+  </si>
+  <si>
+    <t>RX-78GP01</t>
+  </si>
+  <si>
+    <t>Gundam GP01 Zephyranthes</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam 0083: Stardust Memory</t>
+  </si>
+  <si>
+    <t>HGUC #018</t>
+  </si>
+  <si>
+    <t>RX-78GP01-Fb</t>
+  </si>
+  <si>
+    <t>Gundam GP01 Full Burnern</t>
+  </si>
+  <si>
+    <t>HGUC #025</t>
+  </si>
+  <si>
+    <t>RX-78GP03S</t>
+  </si>
+  <si>
+    <t>Gundam GP03S "Stamen"</t>
+  </si>
+  <si>
+    <t>HGUC #074</t>
+  </si>
+  <si>
+    <t>RGM-79Q</t>
+  </si>
+  <si>
+    <t>GM Quel</t>
+  </si>
+  <si>
+    <t>HGUC #113</t>
+  </si>
+  <si>
+    <t>RGM-79C</t>
+  </si>
+  <si>
+    <t>GM Type C</t>
+  </si>
+  <si>
+    <t>HGUC #167</t>
+  </si>
+  <si>
+    <t>F91</t>
+  </si>
+  <si>
+    <t>Gundam F91</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam F91</t>
+  </si>
+  <si>
+    <t>HGUC #100</t>
+  </si>
+  <si>
+    <t>RX-0</t>
+  </si>
+  <si>
+    <t>Unicorn Gundam (Destroy Mode)</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam Unicorn</t>
+  </si>
+  <si>
+    <t>HGUC #123</t>
+  </si>
+  <si>
+    <t>RGM-89De</t>
+  </si>
+  <si>
+    <t>Jegan (ECOAS Type)</t>
+  </si>
+  <si>
+    <t>HGUC #164</t>
+  </si>
+  <si>
+    <t>MSA-003</t>
+  </si>
+  <si>
+    <t>Nemo (Unicorn Desert Color)</t>
+  </si>
+  <si>
+    <t>HGUC #117</t>
+  </si>
+  <si>
+    <t>MS-07B-3</t>
+  </si>
+  <si>
+    <t>Gouf Custom</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam: The 08th MS Team</t>
+  </si>
+  <si>
+    <t>HGUC #210</t>
+  </si>
+  <si>
+    <t>RX-79[G]</t>
+  </si>
+  <si>
+    <t>Gundam Ground Type</t>
+  </si>
+  <si>
+    <t>HGUC #189</t>
+  </si>
+  <si>
+    <t>LM314V23/24</t>
+  </si>
+  <si>
+    <t>V2 Assault Buster Gundam</t>
+  </si>
+  <si>
+    <t>Mobile Suit Victory Gundam</t>
+  </si>
+  <si>
+    <t>HGUC #193</t>
+  </si>
+  <si>
+    <t>RX-178</t>
+  </si>
+  <si>
+    <t>Gundam Mk-II (A.E.U.G.) Revive</t>
+  </si>
+  <si>
+    <t>Mobile Suit Zeta Gundam</t>
+  </si>
+  <si>
+    <t>HGUC #194</t>
+  </si>
+  <si>
+    <t>Gundam Mk-II (Titans)</t>
+  </si>
+  <si>
+    <t>HGUC #255</t>
+  </si>
+  <si>
+    <t>RX-78[G]EX</t>
+  </si>
+  <si>
+    <t>Gundam EX</t>
+  </si>
+  <si>
+    <t>Requiem for Vengeance</t>
+  </si>
+  <si>
+    <t>High Grade (HGWFM) 1/144</t>
+  </si>
+  <si>
+    <t>HGWFM #03</t>
+  </si>
+  <si>
+    <t>XVX-016RN</t>
+  </si>
+  <si>
+    <t>Gundam Aerial</t>
+  </si>
+  <si>
+    <t>The Witch from Mercury</t>
+  </si>
+  <si>
+    <t>Ad Stella (AS)</t>
+  </si>
+  <si>
+    <t>HGWFM #04</t>
+  </si>
+  <si>
+    <t>MSJ-R156</t>
+  </si>
+  <si>
+    <t>Chuchu's Demi Trainer</t>
+  </si>
+  <si>
+    <t>HGWFM #08</t>
+  </si>
+  <si>
+    <t>X-LFRITH</t>
+  </si>
+  <si>
+    <t>Gundam Lfrith Thorn</t>
+  </si>
+  <si>
+    <t>HGWFM #10</t>
+  </si>
+  <si>
+    <t>MSJ-OP16</t>
+  </si>
+  <si>
+    <t>Demi Trainer</t>
+  </si>
+  <si>
+    <t>HGWFM #14</t>
+  </si>
+  <si>
+    <t>System-01</t>
+  </si>
+  <si>
+    <t>Zowort</t>
+  </si>
+  <si>
+    <t>HGWFM #18</t>
+  </si>
+  <si>
+    <t>Gundam Aerial Rebuild</t>
+  </si>
+  <si>
+    <t>HGWFM #22</t>
+  </si>
+  <si>
+    <t>MD-0064</t>
+  </si>
+  <si>
+    <t>Gundam Schwarzette</t>
+  </si>
+  <si>
+    <t>HGWFM #23</t>
+  </si>
+  <si>
+    <t>MDX-0003</t>
+  </si>
+  <si>
+    <t>Demi Barding</t>
+  </si>
+  <si>
+    <t>HGWFM #26</t>
+  </si>
+  <si>
+    <t>X-EX01</t>
+  </si>
+  <si>
+    <t>Gundam Calibarn</t>
+  </si>
+  <si>
+    <t>Macross 1/72 (Hasegawa)</t>
+  </si>
+  <si>
+    <t>Hasegawa #10</t>
+  </si>
+  <si>
+    <t>VF-1</t>
+  </si>
+  <si>
+    <t>VF-1 Battroid Valkyrie</t>
+  </si>
+  <si>
+    <t>Super Dimension Fortress Macross</t>
+  </si>
+  <si>
+    <t>Macross</t>
+  </si>
+  <si>
+    <t>Hasegawa #19</t>
+  </si>
+  <si>
+    <t>VF-1A/J/S</t>
+  </si>
+  <si>
+    <t>VF-1A/J/S Valkyrie</t>
+  </si>
+  <si>
+    <t>Hasegawa #25</t>
+  </si>
+  <si>
+    <t>VF-1J/A</t>
+  </si>
+  <si>
+    <t>VF-1J/A Gerwalk Valkyrie</t>
+  </si>
+  <si>
+    <t>Macross Plus 1/72 (Hasegawa)</t>
+  </si>
+  <si>
+    <t>Hasegawa #09</t>
+  </si>
+  <si>
+    <t>YF-19</t>
+  </si>
+  <si>
+    <t>YF-19 Alpha One</t>
+  </si>
+  <si>
+    <t>Macross Plus</t>
+  </si>
+  <si>
+    <t>Hasegawa #22</t>
+  </si>
+  <si>
+    <t>VF-11B</t>
+  </si>
+  <si>
+    <t>VF-11B Thunderbolt</t>
+  </si>
+  <si>
+    <t>Master Grade (MG) 1/100</t>
+  </si>
+  <si>
+    <t>MG #173</t>
+  </si>
+  <si>
+    <t>Gundam Ver. 3.0</t>
+  </si>
+  <si>
+    <t>MG #122</t>
+  </si>
+  <si>
+    <t>GN-001</t>
+  </si>
+  <si>
+    <t>Gundam Exia</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam 00</t>
+  </si>
+  <si>
+    <t>Anno Domini (AD)</t>
+  </si>
+  <si>
+    <t>MG #018</t>
+  </si>
+  <si>
+    <t>MG #201</t>
+  </si>
+  <si>
+    <t>Gundam F91 Ver.2.0</t>
+  </si>
+  <si>
+    <t>MG #164</t>
+  </si>
+  <si>
+    <t>OZ-00MS</t>
+  </si>
+  <si>
+    <t>Tallgeese EW</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam Wing: EW</t>
+  </si>
+  <si>
+    <t>MG #028</t>
+  </si>
+  <si>
+    <t>MG #031</t>
+  </si>
+  <si>
+    <t>RX-79[G]Ez-8</t>
+  </si>
+  <si>
+    <t>Gundam Ez8</t>
+  </si>
+  <si>
+    <t>MG #038</t>
+  </si>
+  <si>
+    <t>RGM-79[G]</t>
+  </si>
+  <si>
+    <t>GM Ground Type</t>
+  </si>
+  <si>
+    <t>Real Grade (RG) 1/144</t>
+  </si>
+  <si>
+    <t>RG #12</t>
+  </si>
+  <si>
+    <t>RG #03</t>
+  </si>
+  <si>
+    <t>GAT-X105</t>
+  </si>
+  <si>
+    <t>Aile Strike Gundam</t>
+  </si>
+  <si>
+    <t>Mobile Suit Gundam SEED</t>
+  </si>
+  <si>
+    <t>RG #35</t>
+  </si>
+  <si>
+    <t>XXXG-01W</t>
+  </si>
+  <si>
+    <t>Wing Gundam</t>
+  </si>
+  <si>
+    <t>RG #08</t>
+  </si>
+  <si>
+    <t>Gundam Mk-II (A.E.U.G.)</t>
+  </si>
+  <si>
+    <t>Star Wars (Bandai 1/72)</t>
+  </si>
+  <si>
+    <t>Bandai 1/72</t>
+  </si>
+  <si>
+    <t>T-65</t>
+  </si>
+  <si>
+    <t>X-Wing Starfighter</t>
+  </si>
+  <si>
+    <t>Star Wars</t>
+  </si>
+  <si>
+    <t>Star Wars Universe</t>
+  </si>
+  <si>
+    <t>BNS</t>
+  </si>
+  <si>
+    <t>Y-Wing Starfighter</t>
+  </si>
+  <si>
+    <t>Box / Catalog #</t>
+  </si>
+  <si>
+    <t>Nightfall</t>
+  </si>
+  <si>
     <t>XXG-01S</t>
   </si>
   <si>
-    <t>Shenlong Gundam</t>
-  </si>
-  <si>
-    <t>High Grade (HGCE) 1/144</t>
-  </si>
-  <si>
-    <t>HGAC #211</t>
-  </si>
-  <si>
-    <t>OZ-06MS Leo</t>
-  </si>
-  <si>
-    <t>Leo</t>
-  </si>
-  <si>
-    <t>HGCE #201</t>
-  </si>
-  <si>
-    <t>ZGMF-X20A</t>
-  </si>
-  <si>
-    <t>Strike Freedom Gundam</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam SEED DESTINY</t>
-  </si>
-  <si>
-    <t>High Grade (HGGQX) 1/144</t>
-  </si>
-  <si>
-    <t>HGGQX #01</t>
-  </si>
-  <si>
-    <t>GQuuuuux</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam GQuuuuuuX</t>
-  </si>
-  <si>
-    <t>Universal Century (Alternate)</t>
-  </si>
-  <si>
-    <t>High Grade (HGIBO) 1/144</t>
-  </si>
-  <si>
-    <t>HGIBO #001</t>
-  </si>
-  <si>
-    <t>ASW-G-08</t>
-  </si>
-  <si>
-    <t>Gundam Barbatos</t>
-  </si>
-  <si>
-    <t>IRON-BLOODED ORPHANS</t>
-  </si>
-  <si>
-    <t>Post Disaster (PD)</t>
-  </si>
-  <si>
-    <t>High Grade (HGUC) 1/144</t>
-  </si>
-  <si>
-    <t>HGUC #187</t>
-  </si>
-  <si>
-    <t>XM-X1</t>
-  </si>
-  <si>
-    <t>Crossbone Gundam X1</t>
-  </si>
-  <si>
-    <t>Mobile Suit Crossbone Gundam</t>
-  </si>
-  <si>
-    <t>HGUC #020</t>
-  </si>
-  <si>
-    <t>RGM-79</t>
-  </si>
-  <si>
-    <t>GM</t>
-  </si>
-  <si>
-    <t>HGUC #191</t>
-  </si>
-  <si>
-    <t>RX-78-2</t>
-  </si>
-  <si>
-    <t>RX-78-2 Gundam (Revive)</t>
-  </si>
-  <si>
-    <t>HGUC #013</t>
-  </si>
-  <si>
-    <t>RX-78GP01</t>
-  </si>
-  <si>
-    <t>Gundam GP01 Zephyranthes</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam 0083: Stardust Memory</t>
-  </si>
-  <si>
-    <t>HGUC #018</t>
-  </si>
-  <si>
-    <t>RX-78GP01-Fb</t>
-  </si>
-  <si>
-    <t>Gundam GP01 Full Burnern</t>
-  </si>
-  <si>
-    <t>HGUC #025</t>
-  </si>
-  <si>
-    <t>RX-78GP03S</t>
-  </si>
-  <si>
-    <t>Gundam GP03S "Stamen"</t>
-  </si>
-  <si>
-    <t>HGUC #113</t>
-  </si>
-  <si>
-    <t>RGM-79C</t>
-  </si>
-  <si>
-    <t>GM Type C</t>
-  </si>
-  <si>
-    <t>HGUC #167</t>
-  </si>
-  <si>
-    <t>F91</t>
-  </si>
-  <si>
-    <t>Gundam F91</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam F91</t>
-  </si>
-  <si>
-    <t>HGUC #100</t>
-  </si>
-  <si>
-    <t>RX-0</t>
-  </si>
-  <si>
-    <t>Unicorn Gundam (Destroy Mode)</t>
-  </si>
-  <si>
     <t>Mobile Suit Gundam UC</t>
-  </si>
-  <si>
-    <t>HGUC #123</t>
-  </si>
-  <si>
-    <t>RGM-89De</t>
-  </si>
-  <si>
-    <t>Jegan (ECOAS Type)</t>
-  </si>
-  <si>
-    <t>HGUC #117</t>
-  </si>
-  <si>
-    <t>MS-07B-3</t>
-  </si>
-  <si>
-    <t>Gouf Custom</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam: The 08th MS Team</t>
-  </si>
-  <si>
-    <t>HGUC #210</t>
-  </si>
-  <si>
-    <t>RX-79[G]</t>
-  </si>
-  <si>
-    <t>Gundam Ground Type</t>
-  </si>
-  <si>
-    <t>HGUC #189</t>
-  </si>
-  <si>
-    <t>LM314V23/24</t>
-  </si>
-  <si>
-    <t>V2 Assault Buster Gundam</t>
-  </si>
-  <si>
-    <t>Mobile Suit Victory Gundam</t>
-  </si>
-  <si>
-    <t>HGUC #194</t>
-  </si>
-  <si>
-    <t>RX-178</t>
-  </si>
-  <si>
-    <t>Gundam Mk-II (Titans)</t>
-  </si>
-  <si>
-    <t>Mobile Suit Zeta Gundam</t>
-  </si>
-  <si>
-    <t>HGUC #255</t>
-  </si>
-  <si>
-    <t>RX-78[G]EX</t>
-  </si>
-  <si>
-    <t>Gundam EX</t>
-  </si>
-  <si>
-    <t>Requiem for Vengeance</t>
-  </si>
-  <si>
-    <t>High Grade (HGWFM) 1/144</t>
-  </si>
-  <si>
-    <t>HGWFM #04</t>
-  </si>
-  <si>
-    <t>MSJ-R156</t>
-  </si>
-  <si>
-    <t>Chuchu's Demi Trainer</t>
-  </si>
-  <si>
-    <t>The Witch from Mercury</t>
-  </si>
-  <si>
-    <t>Ad Stella (AS)</t>
-  </si>
-  <si>
-    <t>HGWFM #08</t>
-  </si>
-  <si>
-    <t>X-LFRITH</t>
-  </si>
-  <si>
-    <t>Gundam Lfrith Thorn</t>
-  </si>
-  <si>
-    <t>HGWFM #10</t>
-  </si>
-  <si>
-    <t>MSJ-OP16</t>
-  </si>
-  <si>
-    <t>Demi Trainer</t>
-  </si>
-  <si>
-    <t>HGWFM #14</t>
-  </si>
-  <si>
-    <t>System-01</t>
-  </si>
-  <si>
-    <t>Zowort</t>
-  </si>
-  <si>
-    <t>HGWFM #18</t>
-  </si>
-  <si>
-    <t>XVX-016RN</t>
-  </si>
-  <si>
-    <t>Gundam Aerial Rebuild</t>
-  </si>
-  <si>
-    <t>HGWFM #22</t>
-  </si>
-  <si>
-    <t>MD-0064</t>
-  </si>
-  <si>
-    <t>Gundam Schwarzette</t>
-  </si>
-  <si>
-    <t>HGWFM #23</t>
-  </si>
-  <si>
-    <t>MDX-0003</t>
-  </si>
-  <si>
-    <t>Demi Barding</t>
-  </si>
-  <si>
-    <t>HGWFM #26</t>
-  </si>
-  <si>
-    <t>X-EX01</t>
-  </si>
-  <si>
-    <t>Gundam Calibarn</t>
-  </si>
-  <si>
-    <t>Macross 1/72 (Hasegawa)</t>
-  </si>
-  <si>
-    <t>Hasegawa #10</t>
-  </si>
-  <si>
-    <t>VF-1</t>
-  </si>
-  <si>
-    <t>VF-1 Battroid Valkyrie</t>
-  </si>
-  <si>
-    <t>Super Dimension Fortress Macross</t>
-  </si>
-  <si>
-    <t>Macross</t>
-  </si>
-  <si>
-    <t>Hasegawa #19</t>
-  </si>
-  <si>
-    <t>VF-1A/J/S</t>
-  </si>
-  <si>
-    <t>VF-1A/J/S Valkyrie</t>
-  </si>
-  <si>
-    <t>Hasegawa #25</t>
-  </si>
-  <si>
-    <t>VF-1J/A</t>
-  </si>
-  <si>
-    <t>VF-1J/A Gerwalk Valkyrie</t>
-  </si>
-  <si>
-    <t>Macross Plus 1/72 (Hasegawa)</t>
-  </si>
-  <si>
-    <t>Hasegawa #09</t>
-  </si>
-  <si>
-    <t>YF-19</t>
-  </si>
-  <si>
-    <t>YF-19 Alpha One</t>
-  </si>
-  <si>
-    <t>Macross Plus</t>
-  </si>
-  <si>
-    <t>Hasegawa #22</t>
-  </si>
-  <si>
-    <t>VF-11B</t>
-  </si>
-  <si>
-    <t>VF-11B Thunderbolt</t>
-  </si>
-  <si>
-    <t>Master Grade (MG) 1/100</t>
-  </si>
-  <si>
-    <t>MG #173</t>
-  </si>
-  <si>
-    <t>Gundam Ver. 3.0</t>
-  </si>
-  <si>
-    <t>MG #122</t>
-  </si>
-  <si>
-    <t>GN-001</t>
-  </si>
-  <si>
-    <t>Gundam Exia</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam 00</t>
-  </si>
-  <si>
-    <t>Anno Domini (AD)</t>
-  </si>
-  <si>
-    <t>MG #018</t>
-  </si>
-  <si>
-    <t>MG #201</t>
-  </si>
-  <si>
-    <t>Gundam F91 Ver.2.0</t>
-  </si>
-  <si>
-    <t>MG #164</t>
-  </si>
-  <si>
-    <t>OZ-00MS</t>
-  </si>
-  <si>
-    <t>Tallgeese EW</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam Wing: EW</t>
-  </si>
-  <si>
-    <t>MG #028</t>
-  </si>
-  <si>
-    <t>MG #031</t>
-  </si>
-  <si>
-    <t>RX-79[G]Ez-8</t>
-  </si>
-  <si>
-    <t>Gundam Ez8</t>
-  </si>
-  <si>
-    <t>MG #038</t>
-  </si>
-  <si>
-    <t>RGM-79[G]</t>
-  </si>
-  <si>
-    <t>GM Ground Type</t>
-  </si>
-  <si>
-    <t>Real Grade (RG) 1/144</t>
-  </si>
-  <si>
-    <t>RG #03</t>
-  </si>
-  <si>
-    <t>GAT-X105</t>
-  </si>
-  <si>
-    <t>Aile Strike Gundam</t>
-  </si>
-  <si>
-    <t>Mobile Suit Gundam SEED</t>
-  </si>
-  <si>
-    <t>RG #12</t>
-  </si>
-  <si>
-    <t>RG #35</t>
-  </si>
-  <si>
-    <t>XXXG-01W</t>
-  </si>
-  <si>
-    <t>Wing Gundam</t>
-  </si>
-  <si>
-    <t>RG #08</t>
-  </si>
-  <si>
-    <t>Gundam Mk-II (A.E.U.G.)</t>
-  </si>
-  <si>
-    <t>Star Wars (Bandai 1/72)</t>
-  </si>
-  <si>
-    <t>Bandai 1/72</t>
-  </si>
-  <si>
-    <t>T-65</t>
-  </si>
-  <si>
-    <t>X-Wing Starfighter</t>
-  </si>
-  <si>
-    <t>Star Wars</t>
-  </si>
-  <si>
-    <t>Star Wars Universe</t>
-  </si>
-  <si>
-    <t>BNS</t>
-  </si>
-  <si>
-    <t>Y-Wing Starfighter</t>
-  </si>
-  <si>
-    <t>Box / Catalog #</t>
-  </si>
-  <si>
-    <t>Nightfall</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,6 +926,19 @@
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -922,7 +1046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -961,6 +1085,12 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1295,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -1346,245 +1476,245 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" s="2" customFormat="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:26" s="20" customFormat="1">
+      <c r="A2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-    </row>
-    <row r="3" spans="1:26" s="2" customFormat="1">
-      <c r="A3" s="4" t="s">
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+    </row>
+    <row r="3" spans="1:26" s="20" customFormat="1">
+      <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-    </row>
-    <row r="4" spans="1:26" s="2" customFormat="1">
-      <c r="A4" s="4" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+    </row>
+    <row r="4" spans="1:26" s="20" customFormat="1">
+      <c r="A4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-    </row>
-    <row r="5" spans="1:26" s="2" customFormat="1">
-      <c r="A5" s="4" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+    </row>
+    <row r="5" spans="1:26" s="13" customFormat="1">
+      <c r="A5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-    </row>
-    <row r="6" spans="1:26" s="2" customFormat="1">
-      <c r="A6" s="4" t="s">
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+    </row>
+    <row r="6" spans="1:26" s="13" customFormat="1">
+      <c r="A6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-    </row>
-    <row r="7" spans="1:26" s="10" customFormat="1">
-      <c r="A7" s="9" t="s">
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+    </row>
+    <row r="7" spans="1:26" s="20" customFormat="1">
+      <c r="A7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
     </row>
     <row r="8" spans="1:26" s="13" customFormat="1">
       <c r="A8" s="12" t="s">
@@ -1866,45 +1996,45 @@
       <c r="Y14" s="12"/>
       <c r="Z14" s="12"/>
     </row>
-    <row r="15" spans="1:26" s="13" customFormat="1">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:26" s="20" customFormat="1">
+      <c r="A15" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
     </row>
     <row r="16" spans="1:26" s="13" customFormat="1">
       <c r="A16" s="12" t="s">
@@ -1947,22 +2077,22 @@
       <c r="Z16" s="12"/>
     </row>
     <row r="17" spans="1:26" s="10" customFormat="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="12" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="9"/>
@@ -1986,45 +2116,45 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26" s="10" customFormat="1">
-      <c r="A18" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:26" s="20" customFormat="1">
+      <c r="A18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
     </row>
     <row r="19" spans="1:26" s="13" customFormat="1">
       <c r="A19" s="12" t="s">
@@ -2066,64 +2196,64 @@
       <c r="Y19" s="12"/>
       <c r="Z19" s="12"/>
     </row>
-    <row r="20" spans="1:26" s="10" customFormat="1">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:26" s="20" customFormat="1">
+      <c r="A20" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
     </row>
     <row r="21" spans="1:26" s="13" customFormat="1">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>31</v>
+      <c r="E21" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
@@ -2146,64 +2276,64 @@
       <c r="Y21" s="12"/>
       <c r="Z21" s="12"/>
     </row>
-    <row r="22" spans="1:26" s="10" customFormat="1">
-      <c r="A22" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:26" s="13" customFormat="1">
+      <c r="A22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="E22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
+    </row>
+    <row r="23" spans="1:26" s="10" customFormat="1">
+      <c r="A23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="C23" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-    </row>
-    <row r="23" spans="1:26" s="10" customFormat="1">
-      <c r="A23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="D23" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>31</v>
+      <c r="E23" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
@@ -2227,22 +2357,22 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" s="10" customFormat="1">
-      <c r="A24" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G24" s="9"/>
@@ -2266,63 +2396,63 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
     </row>
-    <row r="25" spans="1:26" s="10" customFormat="1">
-      <c r="A25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="9" t="s">
+    <row r="25" spans="1:26" s="20" customFormat="1">
+      <c r="A25" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="D25" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+    </row>
+    <row r="26" spans="1:26" s="10" customFormat="1">
+      <c r="A26" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-    </row>
-    <row r="26" spans="1:26" s="10" customFormat="1">
-      <c r="A26" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="E26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="9"/>
@@ -2346,303 +2476,303 @@
       <c r="Y26" s="9"/>
       <c r="Z26" s="9"/>
     </row>
-    <row r="27" spans="1:26" s="10" customFormat="1">
-      <c r="A27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="9" t="s">
+    <row r="27" spans="1:26" s="20" customFormat="1">
+      <c r="A27" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="19"/>
+    </row>
+    <row r="28" spans="1:26" s="20" customFormat="1">
+      <c r="A28" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="9" t="s">
+      <c r="C28" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-    </row>
-    <row r="28" spans="1:26" s="10" customFormat="1">
-      <c r="A28" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+    </row>
+    <row r="29" spans="1:26" s="20" customFormat="1">
+      <c r="A29" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="F29" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-    </row>
-    <row r="29" spans="1:26" s="10" customFormat="1">
-      <c r="A29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="19"/>
+    </row>
+    <row r="30" spans="1:26" s="20" customFormat="1">
+      <c r="A30" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="C30" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="D30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-    </row>
-    <row r="30" spans="1:26" s="13" customFormat="1">
-      <c r="A30" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="19"/>
+    </row>
+    <row r="31" spans="1:26" s="20" customFormat="1">
+      <c r="A31" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="C31" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F30" s="12" t="s">
+      <c r="D31" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="12"/>
-    </row>
-    <row r="31" spans="1:26" s="10" customFormat="1">
-      <c r="A31" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="19"/>
+    </row>
+    <row r="32" spans="1:26" s="20" customFormat="1">
+      <c r="A32" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="C32" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="D32" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="E32" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-    </row>
-    <row r="32" spans="1:26" s="10" customFormat="1">
-      <c r="A32" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="19"/>
+    </row>
+    <row r="33" spans="1:26" s="20" customFormat="1">
+      <c r="A33" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="F33" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-    </row>
-    <row r="33" spans="1:26" s="10" customFormat="1">
-      <c r="A33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="9" t="s">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="19"/>
+    </row>
+    <row r="34" spans="1:26" s="10" customFormat="1">
+      <c r="A34" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="C34" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="D34" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-    </row>
-    <row r="34" spans="1:26" s="10" customFormat="1">
-      <c r="A34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="9" t="s">
+      <c r="E34" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>31</v>
       </c>
       <c r="G34" s="9"/>
@@ -2666,651 +2796,931 @@
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
     </row>
-    <row r="35" spans="1:26" s="10" customFormat="1">
-      <c r="A35" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="1:26" s="20" customFormat="1">
+      <c r="A35" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="19"/>
+    </row>
+    <row r="36" spans="1:26" s="20" customFormat="1">
+      <c r="A36" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="D36" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E36" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="19"/>
+    </row>
+    <row r="37" spans="1:26" s="20" customFormat="1">
+      <c r="A37" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="C37" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="D37" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-    </row>
-    <row r="36" spans="1:26" s="10" customFormat="1">
-      <c r="A36" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="19"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="19"/>
+    </row>
+    <row r="38" spans="1:26" s="20" customFormat="1">
+      <c r="A38" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="19"/>
+      <c r="Y38" s="19"/>
+      <c r="Z38" s="19"/>
+    </row>
+    <row r="39" spans="1:26" s="20" customFormat="1">
+      <c r="A39" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="19"/>
+    </row>
+    <row r="40" spans="1:26" s="10" customFormat="1">
+      <c r="A40" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" s="20" customFormat="1">
+      <c r="A41" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" s="20" customFormat="1">
+      <c r="A42" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" s="20" customFormat="1">
+      <c r="A43" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" s="20" customFormat="1">
+      <c r="A44" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" s="20" customFormat="1">
+      <c r="A45" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" s="20" customFormat="1">
+      <c r="A46" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" s="20" customFormat="1">
+      <c r="A47" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" s="20" customFormat="1">
+      <c r="A48" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="13" customFormat="1">
+      <c r="A49" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="13" customFormat="1">
+      <c r="A50" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="13" customFormat="1">
+      <c r="A51" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="13" customFormat="1">
+      <c r="A52" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="13" customFormat="1">
+      <c r="A53" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="20" customFormat="1">
+      <c r="A54" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="20" customFormat="1">
+      <c r="A55" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="20" customFormat="1">
+      <c r="A56" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="20" customFormat="1">
+      <c r="A57" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="20" customFormat="1">
+      <c r="A58" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="20" customFormat="1">
+      <c r="A59" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="20" customFormat="1">
+      <c r="A60" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="20" customFormat="1">
+      <c r="A61" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="20" customFormat="1">
+      <c r="A62" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="2" customFormat="1">
+      <c r="A63" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="21" customFormat="1">
+      <c r="A64" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-    </row>
-    <row r="37" spans="1:26" s="10" customFormat="1">
-      <c r="A37" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-    </row>
-    <row r="38" spans="1:26" s="10" customFormat="1">
-      <c r="A38" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-    </row>
-    <row r="39" spans="1:26" s="10" customFormat="1">
-      <c r="A39" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" s="10" customFormat="1">
-      <c r="A40" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B40" s="9" t="s">
+      <c r="F64" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" s="21" customFormat="1">
+      <c r="A65" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+      <c r="V65" s="20"/>
+      <c r="W65" s="20"/>
+      <c r="X65" s="20"/>
+      <c r="Y65" s="20"/>
+      <c r="Z65" s="20"/>
+    </row>
+    <row r="66" spans="1:26" s="21" customFormat="1">
+      <c r="A66" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E66" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" s="10" customFormat="1">
-      <c r="A41" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" s="10" customFormat="1">
-      <c r="A42" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" s="10" customFormat="1">
-      <c r="A43" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B43" s="9" t="s">
+      <c r="F66" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" s="21" customFormat="1">
+      <c r="A67" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" s="17" customFormat="1">
+      <c r="A68" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" s="17" customFormat="1">
+      <c r="A69" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" s="17" customFormat="1">
+      <c r="A70" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" s="17" customFormat="1">
+      <c r="A71" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" s="17" customFormat="1">
+      <c r="A72" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="D72" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="E72" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" s="2" customFormat="1">
-      <c r="A44" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" s="2" customFormat="1">
-      <c r="A45" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" s="2" customFormat="1">
-      <c r="A46" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" s="2" customFormat="1">
-      <c r="A47" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" s="2" customFormat="1">
-      <c r="A48" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" s="10" customFormat="1">
-      <c r="A49" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="9" t="s">
+      <c r="F72" s="21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="10" customFormat="1">
-      <c r="A50" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" s="10" customFormat="1">
-      <c r="A51" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" s="10" customFormat="1">
-      <c r="A52" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" s="10" customFormat="1">
-      <c r="A53" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" s="10" customFormat="1">
-      <c r="A54" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" s="10" customFormat="1">
-      <c r="A55" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" s="10" customFormat="1">
-      <c r="A56" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" s="13" customFormat="1">
-      <c r="A57" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" s="10" customFormat="1">
-      <c r="A58" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" s="10" customFormat="1">
-      <c r="A59" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" s="10" customFormat="1">
-      <c r="A60" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" s="2" customFormat="1">
-      <c r="A61" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" s="2" customFormat="1">
-      <c r="A62" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>233</v>
+    <row r="73" spans="1:26" s="17" customFormat="1">
+      <c r="A73" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" s="17" customFormat="1">
+      <c r="A74" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F62">
-    <sortCondition ref="A2:A62"/>
-    <sortCondition ref="E2:E62"/>
-    <sortCondition ref="B2:B62"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F74">
+    <sortCondition ref="A2:A74"/>
+    <sortCondition ref="E2:E74"/>
+    <sortCondition ref="B2:B74"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3334,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -3379,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>17</v>
@@ -3520,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -3599,142 +4009,142 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="4" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="4" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="4" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="4" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="4" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="4" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="4" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -3744,7 +4154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13620C4F-A8D1-401E-B1F8-EA64F1DF4DFB}">
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.42578125" bestFit="1" customWidth="1"/>
@@ -3760,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -4064,13 +4474,13 @@
         <v>63</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>67</v>
@@ -4105,13 +4515,13 @@
         <v>63</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>67</v>
@@ -4143,16 +4553,16 @@
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>67</v>
@@ -4184,7 +4594,7 @@
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>79</v>
@@ -4307,19 +4717,19 @@
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>31</v>
@@ -4348,16 +4758,16 @@
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>30</v>
@@ -4389,16 +4799,16 @@
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>30</v>
@@ -4430,19 +4840,19 @@
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>31</v>
@@ -4471,19 +4881,19 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>31</v>
@@ -4512,19 +4922,19 @@
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>31</v>
@@ -4553,19 +4963,19 @@
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>31</v>
@@ -4594,19 +5004,19 @@
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>31</v>
@@ -4635,19 +5045,19 @@
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>125</v>
+        <v>274</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>31</v>
@@ -4676,19 +5086,19 @@
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>125</v>
+        <v>274</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>31</v>
@@ -4717,19 +5127,19 @@
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>31</v>
@@ -4758,19 +5168,19 @@
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>31</v>
@@ -4799,19 +5209,19 @@
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>31</v>
@@ -4840,19 +5250,19 @@
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>31</v>
@@ -4881,19 +5291,19 @@
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>31</v>
@@ -4922,22 +5332,22 @@
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
@@ -4963,22 +5373,22 @@
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
@@ -5004,22 +5414,22 @@
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -5045,22 +5455,22 @@
     </row>
     <row r="33" spans="1:27">
       <c r="A33" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
@@ -5086,22 +5496,22 @@
     </row>
     <row r="34" spans="1:27">
       <c r="A34" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
@@ -5127,22 +5537,22 @@
     </row>
     <row r="35" spans="1:27">
       <c r="A35" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
@@ -5168,22 +5578,22 @@
     </row>
     <row r="36" spans="1:27">
       <c r="A36" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
@@ -5209,22 +5619,22 @@
     </row>
     <row r="37" spans="1:27">
       <c r="A37" s="9" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -5248,6 +5658,446 @@
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
     </row>
+    <row r="38" spans="1:27">
+      <c r="A38" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="12"/>
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="12"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+    </row>
+    <row r="39" spans="1:27">
+      <c r="A39" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+    </row>
+    <row r="40" spans="1:27">
+      <c r="A40" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="17"/>
+    </row>
+    <row r="41" spans="1:27">
+      <c r="A41" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+    </row>
+    <row r="42" spans="1:27">
+      <c r="A42" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="17"/>
+    </row>
+    <row r="43" spans="1:27">
+      <c r="A43" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="17"/>
+    </row>
+    <row r="44" spans="1:27">
+      <c r="A44" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="17"/>
+    </row>
+    <row r="45" spans="1:27">
+      <c r="A45" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
+    </row>
+    <row r="46" spans="1:27">
+      <c r="A46" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
+    </row>
+    <row r="47" spans="1:27">
+      <c r="A47" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
+    </row>
+    <row r="48" spans="1:27">
+      <c r="A48" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5271,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -5310,16 +6160,16 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>30</v>
@@ -5351,22 +6201,22 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -5392,19 +6242,19 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>31</v>
@@ -5433,19 +6283,19 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>31</v>
@@ -5474,19 +6324,19 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>68</v>
@@ -5515,19 +6365,19 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>31</v>
@@ -5556,19 +6406,19 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>31</v>
@@ -5597,19 +6447,19 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="9" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>31</v>
@@ -5716,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -5755,19 +6605,19 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="12" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>52</v>
@@ -5796,19 +6646,19 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="9" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>31</v>
@@ -5837,16 +6687,16 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="9" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>67</v>
@@ -5878,19 +6728,19 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="9" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>31</v>
@@ -5943,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
